--- a/site/exports/ecnu-education.xlsx
+++ b/site/exports/ecnu-education.xlsx
@@ -14,11 +14,11 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="来源" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'总览'!$A$1:$K$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'经历'!$A$1:$S$12</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'总览'!$A$1:$K$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'经历'!$A$1:$S$15</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'导师'!$A$1:$L$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'论文'!$A$1:$L$3</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'来源'!$A$1:$G$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'论文'!$A$1:$L$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'来源'!$A$1:$G$5</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -443,18 +443,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K2"/>
+  <dimension ref="A1:K3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="60.2" customWidth="1" min="4" max="4"/>
+    <col width="61.59999999999999" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="65" customWidth="1" min="6" max="6"/>
     <col width="65" customWidth="1" min="7" max="7"/>
-    <col width="26.6" customWidth="1" min="8" max="8"/>
-    <col width="21" customWidth="1" min="9" max="9"/>
+    <col width="40.59999999999999" customWidth="1" min="8" max="8"/>
+    <col width="23.8" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
     <col width="16" customWidth="1" min="11" max="11"/>
   </cols>
@@ -477,7 +477,7 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>官方主页</t>
+          <t>个人主页／职业网站（来源类型见说明）</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
@@ -487,7 +487,7 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>缺项与冲突</t>
+          <t>来源说明与待核事项</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -502,7 +502,7 @@
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>替代官方职业报道（非个人主页）</t>
+          <t>替代职业资料来源（非已核个人主页）</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
@@ -569,10 +569,64 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>王绯烨</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>校区未标注</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>教育学部</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>https://faculty.ecnu.edu.cn/_s8/wfy/main.psp</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>未知（来源日期异常）</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>Partial biography only; degree labels do not establish awards or dates.；Own advisors unknown; coauthors not treated as mentors.；2013.11至今 ECNU segment lacks role and is retained as unclassified, not counted as education.；Current employment and independent directory unknown; bibliography official page only.；Raw necessary professional lines retained immediately, not full HTTP snapshot.</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>分批核实资料，不是完整名录；人物整体核验日期未单独记录</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>官方资料（原来源）；公开个人页（访问与内容时效见来源记录）</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr"/>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>ecnu</t>
+        </is>
+      </c>
+      <c r="K3" s="2" t="inlineStr">
+        <is>
+          <t>华东师范大学</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:K2"/>
+  <autoFilter ref="A1:K3"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D3" r:id="rId2"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -584,13 +638,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S12"/>
+  <dimension ref="A1:S15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
     <col width="40.59999999999999" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="47.59999999999999" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="16" customWidth="1" min="6" max="6"/>
     <col width="26.6" customWidth="1" min="7" max="7"/>
@@ -601,9 +655,9 @@
     <col width="16" customWidth="1" min="12" max="12"/>
     <col width="16" customWidth="1" min="13" max="13"/>
     <col width="16" customWidth="1" min="14" max="14"/>
-    <col width="47.59999999999999" customWidth="1" min="15" max="15"/>
+    <col width="65" customWidth="1" min="15" max="15"/>
     <col width="16" customWidth="1" min="16" max="16"/>
-    <col width="60.2" customWidth="1" min="17" max="17"/>
+    <col width="61.59999999999999" customWidth="1" min="17" max="17"/>
     <col width="16" customWidth="1" min="18" max="18"/>
     <col width="16" customWidth="1" min="19" max="19"/>
   </cols>
@@ -666,7 +720,7 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>确证授位</t>
+          <t>来源记载学位</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
@@ -1424,8 +1478,191 @@
         </is>
       </c>
     </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>王绯烨</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>degree_study</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>硕士</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>北京师范大学教育管理学院</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>2007.9</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>2009.7</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr"/>
+      <c r="H13" s="2" t="inlineStr"/>
+      <c r="I13" s="2" t="inlineStr"/>
+      <c r="J13" s="2" t="inlineStr"/>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr"/>
+      <c r="M13" s="2" t="inlineStr"/>
+      <c r="N13" s="2" t="inlineStr"/>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>本轮按留存来源记录整理；学位资格为来源记载，不代表独立证书认证。</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr"/>
+      <c r="Q13" s="3" t="inlineStr">
+        <is>
+          <t>https://faculty.ecnu.edu.cn/_s8/wfy/main.psp</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>ecnu</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
+        <is>
+          <t>华东师范大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>王绯烨</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>degree_study</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>博士</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>美国佐治亚大学(University of Georgia)教育学院</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>2009.8</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>2013.8</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr"/>
+      <c r="H14" s="2" t="inlineStr"/>
+      <c r="I14" s="2" t="inlineStr"/>
+      <c r="J14" s="2" t="inlineStr"/>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr"/>
+      <c r="M14" s="2" t="inlineStr"/>
+      <c r="N14" s="2" t="inlineStr"/>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>本轮按留存来源记录整理；学位资格为来源记载，不代表独立证书认证。</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr"/>
+      <c r="Q14" s="3" t="inlineStr">
+        <is>
+          <t>https://faculty.ecnu.edu.cn/_s8/wfy/main.psp</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>ecnu</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
+        <is>
+          <t>华东师范大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>王绯烨</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>employment</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>副教授</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>华东师范大学教育学部</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr"/>
+      <c r="F15" s="2" t="inlineStr"/>
+      <c r="G15" s="2" t="inlineStr"/>
+      <c r="H15" s="2" t="inlineStr"/>
+      <c r="I15" s="2" t="inlineStr"/>
+      <c r="J15" s="2" t="inlineStr"/>
+      <c r="K15" s="2" t="inlineStr"/>
+      <c r="L15" s="2" t="inlineStr"/>
+      <c r="M15" s="2" t="inlineStr"/>
+      <c r="N15" s="2" t="inlineStr"/>
+      <c r="O15" s="2" t="inlineStr">
+        <is>
+          <t>任职按留存来源表述保留；不据此认证当前人事状态。；来源role_as_source：副教授；来源institution_as_source：华东师范大学教育学部</t>
+        </is>
+      </c>
+      <c r="P15" s="2" t="inlineStr"/>
+      <c r="Q15" s="3" t="inlineStr">
+        <is>
+          <t>https://faculty.ecnu.edu.cn/_s8/wfy/main.psp</t>
+        </is>
+      </c>
+      <c r="R15" s="2" t="inlineStr">
+        <is>
+          <t>ecnu</t>
+        </is>
+      </c>
+      <c r="S15" s="2" t="inlineStr">
+        <is>
+          <t>华东师范大学</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:S12"/>
+  <autoFilter ref="A1:S15"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q3" r:id="rId2"/>
@@ -1438,6 +1675,9 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q10" r:id="rId9"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q11" r:id="rId10"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q15" r:id="rId14"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1540,16 +1780,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L3"/>
+  <dimension ref="A1:L5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="26.6" customWidth="1" min="2" max="2"/>
+    <col width="32.2" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="60.2" customWidth="1" min="5" max="5"/>
+    <col width="61.59999999999999" customWidth="1" min="5" max="5"/>
     <col width="36.4" customWidth="1" min="6" max="6"/>
-    <col width="60.2" customWidth="1" min="7" max="7"/>
+    <col width="61.59999999999999" customWidth="1" min="7" max="7"/>
     <col width="60.2" customWidth="1" min="8" max="8"/>
     <col width="65" customWidth="1" min="9" max="9"/>
     <col width="65" customWidth="1" min="10" max="10"/>
@@ -1731,8 +1971,112 @@
         </is>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>王绯烨</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>公平视域中基础教育课后服务的价值与实现路径研究</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="n">
+        <v>2023</v>
+      </c>
+      <c r="D4" s="2" t="inlineStr"/>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>https://faculty.ecnu.edu.cn/_s8/wfy/main.psp</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>journal_article</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>https://faculty.ecnu.edu.cn/_s8/wfy/main.psp</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr"/>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>留存来源记载；本轮未重新核验原网页、出版元数据或全文。；source_attributed_recovery_not_reverified</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>留存来源记载；本轮未重新核验原网页、出版元数据或全文。；来源authors_as_source：王萍，王绯烨*，郇松桦，李知源；来源person_contribution_role_as_source：listed author; undefined asterisk not interpreted as corresponding author；来源书目信息（卷）：20；来源书目信息（期）：1；来源书目信息（页码）：5-21</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>ecnu</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>华东师范大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>王绯烨</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>美国新兴教师领导力计划的理念、实操和保障</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="n">
+        <v>2020</v>
+      </c>
+      <c r="D5" s="2" t="inlineStr"/>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>https://faculty.ecnu.edu.cn/_s8/wfy/main.psp</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>journal_article</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>https://faculty.ecnu.edu.cn/_s8/wfy/main.psp</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr"/>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>留存来源记载；本轮未重新核验原网页、出版元数据或全文。；source_attributed_recovery_not_reverified</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>留存来源记载；本轮未重新核验原网页、出版元数据或全文。；来源authors_as_source：王绯烨，洪成文；来源person_contribution_role_as_source：listed author; undefined asterisk not interpreted as corresponding author；来源书目信息（期）：1；来源书目信息（页码）：116-128</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>ecnu</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>华东师范大学</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:L3"/>
+  <autoFilter ref="A1:L5"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G2" r:id="rId2"/>
@@ -1740,6 +2084,10 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E3" r:id="rId4"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G3" r:id="rId5"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H3" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E4" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G4" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E5" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G5" r:id="rId10"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1751,14 +2099,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="37.8" customWidth="1" min="2" max="2"/>
-    <col width="60.2" customWidth="1" min="3" max="3"/>
-    <col width="49" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="65" customWidth="1" min="2" max="2"/>
+    <col width="61.59999999999999" customWidth="1" min="3" max="3"/>
+    <col width="65" customWidth="1" min="4" max="4"/>
+    <col width="28" customWidth="1" min="5" max="5"/>
     <col width="16" customWidth="1" min="6" max="6"/>
     <col width="16" customWidth="1" min="7" max="7"/>
   </cols>
@@ -1911,12 +2259,50 @@
         </is>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>王绯烨</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>new-recovery-ecnu-wangfeiye-education-s001-ae4e76af0cad</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>https://faculty.ecnu.edu.cn/_s8/wfy/main.psp</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>留存来源记录（本轮重新审查；非独立证书认证）；NEW_RECOVERY：依据留存来源摘录、摘要或结构化记录；除另有本轮证据说明外未重新读取原网页，不继承旧核验结论。</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-25T07:53:13Z</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>ecnu</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>华东师范大学</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G4"/>
+  <autoFilter ref="A1:G5"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C3" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C5" r:id="rId4"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
